--- a/data/trans_bre/IQ2606_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 6,26</t>
+          <t>-13,49; 5,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 9,85</t>
+          <t>-8,54; 8,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 14,86</t>
+          <t>-12,78; 16,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 11,8</t>
+          <t>-21,59; 11,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 14,51</t>
+          <t>-11,48; 13,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 19,08</t>
+          <t>-14,2; 22,33</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-10,27</t>
+          <t>-9,96</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-11,62%</t>
+          <t>-11,29%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 17,05</t>
+          <t>1,05; 16,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 9,5</t>
+          <t>-5,27; 8,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 1,55</t>
+          <t>-26,31; 2,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 33,73</t>
+          <t>1,89; 33,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 14,59</t>
+          <t>-7,18; 13,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 1,68</t>
+          <t>-28,37; 3,11</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>-1,32%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 10,24</t>
+          <t>-7,33; 11,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 7,67</t>
+          <t>-6,44; 8,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 13,32</t>
+          <t>-14,06; 11,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 18,1</t>
+          <t>-10,69; 18,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 10,41</t>
+          <t>-8,04; 11,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 16,14</t>
+          <t>-15,27; 14,4</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 16,28</t>
+          <t>-0,71; 16,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 3,28</t>
+          <t>-11,6; 3,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 18,61</t>
+          <t>-12,81; 15,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 32,4</t>
+          <t>-1,16; 33,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 4,65</t>
+          <t>-14,85; 4,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 24,95</t>
+          <t>-14,74; 22,9</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,36%</t>
+          <t>-3,42%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 8,91</t>
+          <t>0,1; 8,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,67</t>
+          <t>-3,85; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,45</t>
+          <t>-9,98; 3,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 16,07</t>
+          <t>0,27; 15,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 5,13</t>
+          <t>-5,16; 4,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 5,39</t>
+          <t>-11,35; 4,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2606_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
+          <t>Menores que el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,14%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-3.648749386702499</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3139523874776895</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.088531455197062</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.06140200309312462</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.004456202117752321</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.01288865353434397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,49; 5,97</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,54; 8,87</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-12,78; 16,52</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-21,59; 11,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-11,48; 13,24</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-14,2; 22,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-13.49012910229361</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.540390845381987</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-12.77811659030728</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.2158782915399083</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1148350176533837</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1419748688186805</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.970111141390415</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.869272532869452</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>16.52054438746069</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.1141128145779163</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1324212511134138</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2232502309094164</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,19</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-9,96</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-11,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 16,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,27; 8,68</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-26,31; 2,67</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,89; 33,01</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,18; 13,18</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-28,37; 3,11</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>9.188163694982077</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.728208847658463</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-9.957567194563877</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.1683307903922197</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.02475916618473319</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1129474459446694</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,32%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.050753118674811</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.273515012519545</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-26.30508628870664</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.01893408039460052</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.0717569194593394</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2836502151171619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,33; 11,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,44; 8,37</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-14,06; 11,93</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-10,69; 18,93</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-8,04; 11,29</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-15,27; 14,4</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>16.40856937816092</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.682879054206337</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.671249217125264</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.3300931677433283</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1317827658764885</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03108201525261279</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,61</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-4,07</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-5,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.866538601356982</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9859755822019589</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.175919621571986</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.02930570187350311</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.01266796394325423</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.01320907619069312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,71; 16,23</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-11,6; 3,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-12,81; 15,97</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,16; 33,63</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-14,85; 4,45</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-14,74; 22,9</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.331372187348214</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.444578165329886</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-14.06155958243699</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.1068755657120117</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.08044357228245819</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1527080745478287</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.06995977189819</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.366651791482219</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>11.93116293843531</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.1893041768915009</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1129151157542055</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1440171052088853</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.613172996215889</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-4.070132974871843</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.607870691300162</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.1393134162826304</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.05370094512226624</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.02003041580726867</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.7149647701362523</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-11.59965532335673</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-12.80716684711239</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.01163499390023631</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1484516597520508</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1474498288731095</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>16.22865082419348</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.224448348677415</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>15.96940265641534</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.3363133928026571</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04449983732240237</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2290494523935013</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,46%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-3,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 8,53</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 3,52</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-9,98; 3,72</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,27; 15,37</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 4,93</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-11,35; 4,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>4.547836484341872</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3351055993549013</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.929035505774136</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.07899652103885399</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.004566435591841512</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.03418950440371978</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1008196889340038</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.854760058914387</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.980223839079811</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.002726308143434902</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.05163330710970351</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1135236177208179</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.534949840903913</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.520854276043286</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.723646708124626</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.1537358137930534</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.04932372641546322</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.0458041531729814</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
